--- a/data/Bowil/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Bowil/investment_decision/aggregated_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K221"/>
+  <dimension ref="A1:K226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,32 +455,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,25 +499,25 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>3285.463865861201</v>
+        <v>1489.109757465916</v>
       </c>
       <c r="D2" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="E2" t="n">
-        <v>3288.700853021371</v>
+        <v>1501.153517003432</v>
       </c>
       <c r="F2" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="G2" t="n">
-        <v>3122.635854415639</v>
+        <v>1489.476415074285</v>
       </c>
       <c r="H2" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="I2" t="n">
-        <v>3088.728797513608</v>
+        <v>1501.611689791432</v>
       </c>
       <c r="J2" t="n">
         <v>559891.4401873931</v>
@@ -536,25 +536,25 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>3501.197694801776</v>
+        <v>1743.383547924486</v>
       </c>
       <c r="D3" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="E3" t="n">
-        <v>3504.864385747121</v>
+        <v>1761.068246288377</v>
       </c>
       <c r="F3" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="G3" t="n">
-        <v>3354.909617348458</v>
+        <v>1744.518798990209</v>
       </c>
       <c r="H3" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="I3" t="n">
-        <v>3318.396549663653</v>
+        <v>1764.661603758974</v>
       </c>
       <c r="J3" t="n">
         <v>559891.4401873931</v>
@@ -573,25 +573,25 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>3630.415387311734</v>
+        <v>2026.959332481384</v>
       </c>
       <c r="D4" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="E4" t="n">
-        <v>3633.288367062423</v>
+        <v>2024.854364384486</v>
       </c>
       <c r="F4" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="G4" t="n">
-        <v>3472.882276211275</v>
+        <v>2025.013075760619</v>
       </c>
       <c r="H4" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="I4" t="n">
-        <v>3433.118950306671</v>
+        <v>2038.130064657736</v>
       </c>
       <c r="J4" t="n">
         <v>559891.4401873931</v>
@@ -610,25 +610,25 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>3925.418978175112</v>
+        <v>2027.075440818407</v>
       </c>
       <c r="D5" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="E5" t="n">
-        <v>3741.28621184093</v>
+        <v>2025.123708143815</v>
       </c>
       <c r="F5" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="G5" t="n">
-        <v>3472.882276211275</v>
+        <v>2025.175786031458</v>
       </c>
       <c r="H5" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="I5" t="n">
-        <v>3433.118950306671</v>
+        <v>2038.132993718293</v>
       </c>
       <c r="J5" t="n">
         <v>559891.4401873931</v>
@@ -647,25 +647,25 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>3937.511946922444</v>
+        <v>2044.373776204319</v>
       </c>
       <c r="D6" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="E6" t="n">
-        <v>3749.991851770366</v>
+        <v>2045.033740003944</v>
       </c>
       <c r="F6" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="G6" t="n">
-        <v>3478.428526616207</v>
+        <v>2026.182094734442</v>
       </c>
       <c r="H6" t="n">
         <v>559891.4401873931</v>
       </c>
       <c r="I6" t="n">
-        <v>3440.404336911167</v>
+        <v>2045.911243310619</v>
       </c>
       <c r="J6" t="n">
         <v>559891.4401873931</v>
@@ -677,7 +677,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -687,34 +687,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>839.8371602810896</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>839.8371602810896</v>
+        <v>369.3680485313439</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>452.1316285243195</v>
+        <v>369.3680485313439</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>452.1316285243195</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -724,34 +724,34 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>839.8371602810896</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>839.8371602810896</v>
+        <v>481.3116612221986</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>591.800989564387</v>
+        <v>481.3116612221986</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>591.800989564387</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -761,34 +761,34 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>839.8371602810896</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>839.8371602810896</v>
+        <v>533.2254709708988</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>656.5726050453026</v>
+        <v>533.2254709708988</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>656.5726050453026</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -798,34 +798,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>839.8371602810896</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>839.8371602810896</v>
+        <v>562.5161530734653</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>693.117886686257</v>
+        <v>562.5161530734653</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>693.117886686257</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -835,28 +835,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>839.8371602810896</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>839.8371602810896</v>
+        <v>581.181210313564</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>716.4058309989014</v>
+        <v>581.181210313564</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>716.4058309989014</v>
+        <v>680.1102010112359</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>13.50077428084194</v>
+        <v>3.627715470953039</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.627715470953039</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>13.50077428084194</v>
+        <v>5.466261685265637</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>5.466261685265637</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13.50077428084194</v>
+        <v>6.552464892610645</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6.552464892610645</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>13.50077428084194</v>
+        <v>7.261818112236187</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7.261818112236187</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>13.50077428084194</v>
+        <v>7.759004308360768</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>7.759004308360768</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2958608417691728</v>
+        <v>0.4482317528944757</v>
       </c>
       <c r="D17" t="n">
         <v>13.50077428084194</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2958608417691729</v>
+        <v>0.4485311758352941</v>
       </c>
       <c r="F17" t="n">
-        <v>13.50077428084194</v>
+        <v>3.627715470953039</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2959021765717701</v>
+        <v>0.4485311758352941</v>
       </c>
       <c r="H17" t="n">
         <v>3.627715470953039</v>
       </c>
       <c r="I17" t="n">
-        <v>0.29590217657177</v>
+        <v>0.4486549438574566</v>
       </c>
       <c r="J17" t="n">
-        <v>3.627715470953039</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2983158836707512</v>
+        <v>0.4928814884265745</v>
       </c>
       <c r="D18" t="n">
         <v>13.50077428084194</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2983951390025035</v>
+        <v>0.5005478105647059</v>
       </c>
       <c r="F18" t="n">
-        <v>13.50077428084194</v>
+        <v>5.466261685265637</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2984335932396678</v>
+        <v>0.4967816207164508</v>
       </c>
       <c r="H18" t="n">
         <v>5.466261685265637</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2984335932396679</v>
+        <v>0.4947913845398095</v>
       </c>
       <c r="J18" t="n">
-        <v>5.466261685265637</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3014410120617586</v>
+        <v>0.5158535072</v>
       </c>
       <c r="D19" t="n">
         <v>13.50077428084194</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3016110627816835</v>
+        <v>0.5248550648627531</v>
       </c>
       <c r="F19" t="n">
-        <v>13.50077428084194</v>
+        <v>6.552464892610645</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3016110627816835</v>
+        <v>0.5244378552828998</v>
       </c>
       <c r="H19" t="n">
         <v>6.552464892610645</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3016110627816835</v>
+        <v>0.5158535072</v>
       </c>
       <c r="J19" t="n">
-        <v>6.552464892610645</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3015118433328367</v>
+        <v>0.5162758333638746</v>
       </c>
       <c r="D20" t="n">
         <v>13.50077428084194</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3016110627816834</v>
+        <v>0.5249944786581644</v>
       </c>
       <c r="F20" t="n">
-        <v>13.50077428084194</v>
+        <v>7.261818112236187</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3016174648903561</v>
+        <v>0.5249383000515586</v>
       </c>
       <c r="H20" t="n">
         <v>7.261818112236187</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3016174648903562</v>
+        <v>0.5167302557645366</v>
       </c>
       <c r="J20" t="n">
-        <v>7.261818112236187</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2992389967668052</v>
+        <v>0.5162758333638746</v>
       </c>
       <c r="D21" t="n">
         <v>13.50077428084194</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2992389967668053</v>
+        <v>0.5249094822588183</v>
       </c>
       <c r="F21" t="n">
-        <v>13.50077428084194</v>
+        <v>7.759004308360768</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3002391552600037</v>
+        <v>0.5248918553651489</v>
       </c>
       <c r="H21" t="n">
         <v>7.759004308360768</v>
       </c>
       <c r="I21" t="n">
-        <v>0.299240243306505</v>
+        <v>0.5261597521393908</v>
       </c>
       <c r="J21" t="n">
-        <v>7.759004308360768</v>
+        <v>13.50077428084194</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1094155916640076</v>
+        <v>0.09884604139301278</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1094155916640076</v>
+        <v>0.0986823154876926</v>
       </c>
       <c r="F22" t="n">
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1094570362964706</v>
+        <v>0.09898258018823529</v>
       </c>
       <c r="H22" t="n">
         <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1094570362964706</v>
+        <v>0.0990073337926678</v>
       </c>
       <c r="J22" t="n">
         <v>9</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1104470435645525</v>
+        <v>0.1033845242541176</v>
       </c>
       <c r="D23" t="n">
         <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.112747091700297</v>
+        <v>0.1041352842799982</v>
       </c>
       <c r="F23" t="n">
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1128079549000726</v>
+        <v>0.10413528428</v>
       </c>
       <c r="H23" t="n">
         <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1112613498511331</v>
+        <v>0.1038080591234131</v>
       </c>
       <c r="J23" t="n">
         <v>9</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1189049180882502</v>
+        <v>0.105689914976685</v>
       </c>
       <c r="D24" t="n">
         <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1197059472362894</v>
+        <v>0.1062617005182323</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1197253658036021</v>
+        <v>0.1062509922043555</v>
       </c>
       <c r="H24" t="n">
         <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1197051935729561</v>
+        <v>0.1058095898342656</v>
       </c>
       <c r="J24" t="n">
         <v>9</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1223254661497035</v>
+        <v>0.105689914976685</v>
       </c>
       <c r="D25" t="n">
         <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1230063981423407</v>
+        <v>0.1062617005182323</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1243354458284028</v>
+        <v>0.1062509922043555</v>
       </c>
       <c r="H25" t="n">
         <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1241206149101236</v>
+        <v>0.1058095898342656</v>
       </c>
       <c r="J25" t="n">
         <v>9</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1235662103799574</v>
+        <v>0.105689914976685</v>
       </c>
       <c r="D26" t="n">
         <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1237962009864591</v>
+        <v>0.1062617005182323</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1250988727004403</v>
+        <v>0.1062579422569474</v>
       </c>
       <c r="H26" t="n">
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1249041124149245</v>
+        <v>0.1058095898342656</v>
       </c>
       <c r="J26" t="n">
         <v>9</v>
@@ -1602,7 +1602,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.0488804107201733</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1630,16 +1630,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0488804107201733</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -1649,13 +1649,13 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.08192846775049219</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1667,16 +1667,16 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.08192846775049219</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1686,13 +1686,13 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.1064719951694473</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1704,16 +1704,16 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1064719951694473</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -1723,13 +1723,13 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.1257660092222253</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1257660092222253</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1760,13 +1760,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.1415431203502453</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1415431203502453</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="37">
@@ -1794,28 +1794,28 @@
         <v>46023</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01245209280235546</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01245209280235546</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01245398239333134</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0124539823933313</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="K37" t="n">
         <v>175</v>
@@ -1831,28 +1831,28 @@
         <v>47849</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0129945753901251</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0129981984910052</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01299995639898986</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01299995639898986</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="K38" t="n">
         <v>175</v>
@@ -1868,28 +1868,28 @@
         <v>49675</v>
       </c>
       <c r="C39" t="n">
-        <v>0.01356307462410506</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01357728665562655</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01358172518529802</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0135771143897218</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="K39" t="n">
         <v>175</v>
@@ -1905,28 +1905,28 @@
         <v>51502</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01417670799614541</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01432781384822948</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01463130350864722</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01458219929875482</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="K40" t="n">
         <v>175</v>
@@ -1942,28 +1942,28 @@
         <v>53328</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0145642082346506</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0146167775161367</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01487410965658925</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01486995742939966</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>9.598138974641024</v>
+        <v>9.598138974641023</v>
       </c>
       <c r="K41" t="n">
         <v>175</v>
@@ -1972,7 +1972,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1982,34 +1982,34 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.039316756353022</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1.039316756353022</v>
+        <v>0.04035015582732388</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01513130843524646</v>
+        <v>0.04035015582732388</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01513130843524646</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2019,145 +2019,145 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.039316756353022</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.039316756353022</v>
+        <v>0.07119487229845679</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0266980771119213</v>
+        <v>0.07119487229845679</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0266980771119213</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1.039316756353022</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1.039316756353022</v>
+        <v>0.09670962609505708</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.03626610978564641</v>
+        <v>0.09670962609505708</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.03626610978564641</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>1.039316756353022</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1.039316756353022</v>
+        <v>0.118659479158747</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04449730468453011</v>
+        <v>0.118659479158747</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04449730468453011</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1.039316756353022</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>1.039316756353022</v>
+        <v>0.1380098287838563</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05175368579394611</v>
+        <v>0.1380098287838563</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0.05175368579394611</v>
+        <v>2.771511350274725</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>2.003502180921488</v>
+        <v>0.02916878734505341</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.02916878734505341</v>
+        <v>2.003502180921488</v>
       </c>
       <c r="K47" t="n">
         <v>4.15</v>
@@ -2194,7 +2194,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2210,19 +2210,19 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
+        <v>0.0514661727458724</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.0514661727458724</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>2.003502180921488</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.05146617274587239</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.05146617274587239</v>
       </c>
       <c r="K48" t="n">
         <v>4.15</v>
@@ -2231,7 +2231,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>2.003502180921488</v>
+        <v>0.06991057308076418</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06991057308076418</v>
+        <v>2.003502180921488</v>
       </c>
       <c r="K49" t="n">
         <v>4.15</v>
@@ -2268,7 +2268,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2284,19 +2284,19 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
+        <v>0.0857779367412629</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0857779367412629</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>2.003502180921488</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.08577793674126288</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.08577793674126288</v>
       </c>
       <c r="K50" t="n">
         <v>4.15</v>
@@ -2305,7 +2305,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -2321,19 +2321,19 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
+        <v>0.09976614128953469</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.09976614128953469</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>2.003502180921488</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.09976614128953468</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.09976614128953468</v>
       </c>
       <c r="K51" t="n">
         <v>4.15</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02771511350274725</v>
+        <v>0.0004035015582732388</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0004035015582732388</v>
+        <v>0.02771511350274725</v>
       </c>
       <c r="K52" t="n">
         <v>300</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.02771511350274725</v>
+        <v>0.0007119487229845681</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0007119487229845681</v>
+        <v>0.02771511350274725</v>
       </c>
       <c r="K53" t="n">
         <v>300</v>
@@ -2432,19 +2432,19 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
+        <v>0.000967096260950571</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.000967096260950571</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.02771511350274725</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.0009670962609505709</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.0009670962609505709</v>
       </c>
       <c r="K54" t="n">
         <v>300</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02771511350274725</v>
+        <v>0.00118659479158747</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00118659479158747</v>
+        <v>0.02771511350274725</v>
       </c>
       <c r="K55" t="n">
         <v>300</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02771511350274725</v>
+        <v>0.001380098287838563</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.001380098287838563</v>
+        <v>0.02771511350274725</v>
       </c>
       <c r="K56" t="n">
         <v>300</v>
@@ -2527,7 +2527,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -2537,34 +2537,34 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>0.2421009349639433</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>0.2421009349639433</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2574,34 +2574,34 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>0.4271692337907408</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>0.4271692337907408</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -2611,34 +2611,34 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>0.5802577565703426</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>0.5802577565703426</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2648,34 +2648,34 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>0.7119568749524819</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>0.7119568749524819</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -2685,34 +2685,34 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>0.8280589727031379</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>0.8280589727031379</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>16.62906810164835</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2743,13 +2743,13 @@
         <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -2780,13 +2780,13 @@
         <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2817,13 +2817,13 @@
         <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -2854,13 +2854,13 @@
         <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2891,568 +2891,568 @@
         <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4709031034493787</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="E67" t="n">
-        <v>0.483275518096749</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4079679575636181</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4256161103391174</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7792080207933785</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7436679131638562</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5862438018807252</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6038919546562245</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="K68" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7792080207933785</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7436679131638562</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>0.5862438018807252</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6038919546562245</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="K69" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4614737589735221</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="E70" t="n">
-        <v>0.3891247347558245</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2510049609288298</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2738307459959983</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="K70" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3174019431295221</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2929654411887171</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>0.1558481129577443</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1765413932937936</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>4.460141868</v>
+        <v>100</v>
       </c>
       <c r="K71" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5156755302995791</v>
+        <v>0.6930140254980092</v>
       </c>
       <c r="D72" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5156755302995741</v>
+        <v>0.6400837796990694</v>
       </c>
       <c r="F72" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5156755302995767</v>
+        <v>0.6397902404099469</v>
       </c>
       <c r="H72" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5156755302995691</v>
+        <v>0.6741558298071805</v>
       </c>
       <c r="J72" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K72" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5156755302995791</v>
+        <v>1.465650551933417</v>
       </c>
       <c r="D73" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5156755302995741</v>
+        <v>1.366596591166314</v>
       </c>
       <c r="F73" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5156755302995767</v>
+        <v>1.366037061586762</v>
       </c>
       <c r="H73" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5156755302995691</v>
+        <v>1.443775220370436</v>
       </c>
       <c r="J73" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K73" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5926244502995791</v>
+        <v>1.465650551933417</v>
       </c>
       <c r="D74" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5926244502995741</v>
+        <v>1.366596591166314</v>
       </c>
       <c r="F74" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5926244502995671</v>
+        <v>1.366037061586762</v>
       </c>
       <c r="H74" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5926244502995691</v>
+        <v>1.443775220370436</v>
       </c>
       <c r="J74" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K74" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.181949149542898</v>
       </c>
       <c r="D75" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.105260795306954</v>
       </c>
       <c r="F75" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.120550147123381</v>
       </c>
       <c r="H75" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.170658086801902</v>
       </c>
       <c r="J75" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K75" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.126867347189276</v>
       </c>
       <c r="D76" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.024932990115953</v>
       </c>
       <c r="F76" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G76" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.041651882391464</v>
       </c>
       <c r="H76" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1677879832519835</v>
+        <v>1.118917222858097</v>
       </c>
       <c r="J76" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K76" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>0.3085487770007512</v>
       </c>
       <c r="D77" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>0.2993331462449328</v>
       </c>
       <c r="F77" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.2993331462449328</v>
       </c>
       <c r="H77" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>0.3154753855288899</v>
       </c>
       <c r="J77" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K77" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.6705709577154103</v>
       </c>
       <c r="D78" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>0.6221511365381415</v>
       </c>
       <c r="F78" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>0.6221511365381531</v>
       </c>
       <c r="H78" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>0.6709824148078224</v>
       </c>
       <c r="J78" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K78" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>7.260621791590367</v>
       </c>
       <c r="D79" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>6.743842264232022</v>
       </c>
       <c r="F79" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>6.74530629331821</v>
       </c>
       <c r="H79" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>7.488426345043396</v>
       </c>
       <c r="J79" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K79" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>8.161828775065542</v>
       </c>
       <c r="D80" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>7.328203940567072</v>
       </c>
       <c r="F80" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>7.327838965690994</v>
       </c>
       <c r="H80" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>8.059728896965863</v>
       </c>
       <c r="J80" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K80" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>8.174133444505214</v>
       </c>
       <c r="D81" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>7.328203940567072</v>
       </c>
       <c r="F81" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>7.327838965690994</v>
       </c>
       <c r="H81" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>8.078987061582142</v>
       </c>
       <c r="J81" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K81" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3462,34 +3462,34 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K82" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -3499,34 +3499,34 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K83" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -3536,34 +3536,34 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K84" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -3573,34 +3573,34 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K85" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -3610,34 +3610,34 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K86" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -3647,34 +3647,34 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K87" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -3684,34 +3684,34 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K88" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -3721,34 +3721,34 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K89" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -3758,34 +3758,34 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K90" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -3795,34 +3795,34 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K91" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -3832,367 +3832,367 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K92" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.0255528</v>
       </c>
       <c r="D93" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.03564369215102395</v>
       </c>
       <c r="F93" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.03590968244145251</v>
       </c>
       <c r="H93" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>0.02556220486072514</v>
       </c>
       <c r="J93" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K93" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.02628500369624729</v>
       </c>
       <c r="D94" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>0.03667616611005245</v>
       </c>
       <c r="F94" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>0.03683936844813025</v>
       </c>
       <c r="H94" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>0.0271581819596079</v>
       </c>
       <c r="J94" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K94" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.0262850036962473</v>
       </c>
       <c r="D95" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>0.03667616611005245</v>
       </c>
       <c r="F95" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.03683936844813026</v>
       </c>
       <c r="H95" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>0.0271581819596079</v>
       </c>
       <c r="J95" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K95" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.0146016</v>
       </c>
       <c r="D96" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>0.0859607554926369</v>
       </c>
       <c r="F96" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>0.1106347885638145</v>
       </c>
       <c r="H96" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>0.01492090923818518</v>
       </c>
       <c r="J96" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K96" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.01628884292494991</v>
       </c>
       <c r="D97" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.02520959672618279</v>
       </c>
       <c r="F97" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.02520959672618286</v>
       </c>
       <c r="H97" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>0.009362234396811197</v>
       </c>
       <c r="J97" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K97" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.03882492271374655</v>
       </c>
       <c r="D98" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>0.06372832187367164</v>
       </c>
       <c r="F98" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>0.0637405376271049</v>
       </c>
       <c r="H98" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>0.03450336514523342</v>
       </c>
       <c r="J98" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K98" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.241467919796378</v>
       </c>
       <c r="D99" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>0.6346107091662172</v>
       </c>
       <c r="F99" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.6305941912701587</v>
       </c>
       <c r="H99" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>0.265019594695042</v>
       </c>
       <c r="J99" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K99" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.2251790768714281</v>
       </c>
       <c r="D100" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>0.6442733473317354</v>
       </c>
       <c r="F100" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>0.643737520845083</v>
       </c>
       <c r="H100" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>0.2556573602982308</v>
       </c>
       <c r="J100" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K100" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.2128744074317551</v>
       </c>
       <c r="D101" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.6541650453124654</v>
       </c>
       <c r="F101" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>0.6540413264562419</v>
       </c>
       <c r="H101" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>0.2353349974608515</v>
       </c>
       <c r="J101" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K101" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -4202,34 +4202,34 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K102" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -4239,34 +4239,34 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K103" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -4276,34 +4276,34 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K104" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -4313,34 +4313,34 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K105" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -4350,34 +4350,34 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K106" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K107" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -4424,34 +4424,34 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K108" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -4461,34 +4461,34 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K109" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -4498,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K110" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -4535,34 +4535,34 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>4.460141868</v>
+        <v>61.491873492</v>
       </c>
       <c r="K111" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -4572,34 +4572,34 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K112" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -4609,34 +4609,34 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K113" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -4646,34 +4646,34 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K114" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -4683,34 +4683,34 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K115" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -4720,34 +4720,34 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>61.491873492</v>
+        <v>4.460141868</v>
       </c>
       <c r="K116" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -4757,182 +4757,182 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C118" t="n">
-        <v>13.89221501885753</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="E118" t="n">
-        <v>13.88811069258279</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="G118" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="I118" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C119" t="n">
-        <v>16.51170374383661</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="E119" t="n">
-        <v>16.51364529821885</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="G119" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="I119" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C120" t="n">
-        <v>20.60907128447333</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="E120" t="n">
-        <v>20.58931093824157</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="G120" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="I120" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C121" t="n">
-        <v>21.04672563911254</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="E121" t="n">
-        <v>20.94823735405875</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>28.83402398829847</v>
+        <v>61.491873492</v>
       </c>
       <c r="G121" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="I121" t="n">
-        <v>2.565588729494484</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>2.565588729494484</v>
+        <v>61.491873492</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -4942,182 +4942,182 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>258.6425246212957</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>258.6425246212957</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>116.0870397010226</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>116.0870397010226</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="K122" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>15.78432388780318</v>
       </c>
       <c r="D123" t="n">
-        <v>258.6425246212957</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="F123" t="n">
-        <v>258.6425246212957</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="H123" t="n">
-        <v>158.0583110467957</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>15.88104886280528</v>
       </c>
       <c r="J123" t="n">
-        <v>158.0583110467957</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="K123" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>17.92304210525085</v>
       </c>
       <c r="D124" t="n">
-        <v>258.6425246212957</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="F124" t="n">
-        <v>258.6425246212957</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="H124" t="n">
-        <v>179.7683175006073</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>16.51093227983141</v>
       </c>
       <c r="J124" t="n">
-        <v>179.7683175006073</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="K124" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>17.92304210525085</v>
       </c>
       <c r="D125" t="n">
-        <v>258.6425246212957</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="F125" t="n">
-        <v>258.6425246212957</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="H125" t="n">
-        <v>192.8687972524032</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>17.14045156474375</v>
       </c>
       <c r="J125" t="n">
-        <v>192.8687972524032</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="K125" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>20.51033547374807</v>
       </c>
       <c r="D126" t="n">
-        <v>258.6425246212957</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="F126" t="n">
-        <v>258.6425246212957</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="H126" t="n">
-        <v>201.606330874373</v>
+        <v>2.565588729494484</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>18.70899392925524</v>
       </c>
       <c r="J126" t="n">
-        <v>201.606330874373</v>
+        <v>28.83402398829847</v>
       </c>
       <c r="K126" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -5127,34 +5127,34 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>17.76982512623477</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>17.76982512623477</v>
+        <v>116.0870397010226</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>8.082313240008761</v>
+        <v>116.0870397010226</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>8.082313240008761</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="K127" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -5164,34 +5164,34 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>17.76982512623477</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>17.76982512623477</v>
+        <v>158.0583110467957</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>10.93451629813445</v>
+        <v>158.0583110467957</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>10.93451629813445</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="K128" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -5201,34 +5201,34 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>17.76982512623477</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>17.76982512623477</v>
+        <v>179.7683175006073</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>12.40984322567405</v>
+        <v>179.7683175006073</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>12.40984322567405</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="K129" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -5238,34 +5238,34 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>17.76982512623477</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>17.76982512623477</v>
+        <v>192.8687972524032</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>13.3001004709969</v>
+        <v>192.8687972524032</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>13.3001004709969</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="K130" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -5275,34 +5275,34 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>17.76982512623477</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>17.76982512623477</v>
+        <v>201.606330874373</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>13.89386900166039</v>
+        <v>201.606330874373</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>13.89386900166039</v>
+        <v>258.6425246212957</v>
       </c>
       <c r="K131" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -5312,478 +5312,478 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>2.424242424242424</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>2.424242424242424</v>
+        <v>8.082313240008761</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>8.082313240008761</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="K132" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>2.424242424242424</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>2.424242424242424</v>
+        <v>10.93451629813445</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>10.93451629813445</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="K133" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>2.424242424242424</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>2.424242424242424</v>
+        <v>12.40984322567405</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>12.40984322567405</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="K134" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>2.424242424242424</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>2.424242424242424</v>
+        <v>13.3001004709969</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>13.3001004709969</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="K135" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>2.424242424242424</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>2.424242424242424</v>
+        <v>13.89386900166039</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>13.89386900166039</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>17.76982512623477</v>
       </c>
       <c r="K136" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C137" t="n">
-        <v>0.09808461548393752</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1290015258642789</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1325465822648293</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1022640061026265</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="K137" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C138" t="n">
-        <v>0.09808461548393752</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1290015258642789</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.1325465822648293</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1022640061026265</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="K138" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C139" t="n">
-        <v>0.09808461548393752</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1290015258642789</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.1325465822648293</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1022640061026265</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="K139" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="K140" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>619.5123239502191</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
-        <v>619.5123239502191</v>
+        <v>2.424242424242424</v>
       </c>
       <c r="K141" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>0.1082737313277888</v>
       </c>
       <c r="D142" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>0.1377791344318943</v>
       </c>
       <c r="F142" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>0.1082846095854808</v>
       </c>
       <c r="H142" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>0.1384906651993683</v>
       </c>
       <c r="J142" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K142" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>0.1082737313277888</v>
       </c>
       <c r="D143" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>0.1377791344318943</v>
       </c>
       <c r="F143" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>0.1082846095854808</v>
       </c>
       <c r="H143" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>0.1384906651993683</v>
       </c>
       <c r="J143" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K143" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>0.1082737313277888</v>
       </c>
       <c r="D144" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>0.1377791344318943</v>
       </c>
       <c r="F144" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>0.1082846095854808</v>
       </c>
       <c r="H144" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>0.1384906651993683</v>
       </c>
       <c r="J144" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K144" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
@@ -5793,34 +5793,34 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K145" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
@@ -5830,404 +5830,404 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K146" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>104.5286644784412</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E147" t="n">
-        <v>87.57574934421889</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G147" t="n">
-        <v>108.694247631957</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>183.997094408346</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I147" t="n">
-        <v>115.8289232145284</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>183.997094408346</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K147" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>114.578795571987</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E148" t="n">
-        <v>97.34202561813505</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G148" t="n">
-        <v>118.3030365522152</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>262.7193286077312</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I148" t="n">
-        <v>125.7719157215994</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>262.7193286077312</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K148" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>189.6120231694895</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E149" t="n">
-        <v>170.7087446333443</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G149" t="n">
-        <v>192.4761070151336</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>305.5216950259997</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I149" t="n">
-        <v>201.656564953641</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>305.5216950259997</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K149" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>219.9540789710034</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E150" t="n">
-        <v>212.4301245146287</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G150" t="n">
-        <v>211.5602433393984</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>331.8698213388956</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I150" t="n">
-        <v>218.4606244162425</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>331.8698213388956</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K150" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>218.3027088494337</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E151" t="n">
-        <v>211.3042525527439</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G151" t="n">
-        <v>210.1852069258329</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>349.5634898849344</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I151" t="n">
-        <v>216.6142210914907</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>349.5634898849344</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K151" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>97.60266946517946</v>
       </c>
       <c r="D152" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>69.42770687711504</v>
       </c>
       <c r="F152" t="n">
-        <v>30.23034750990276</v>
+        <v>183.997094408346</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>92.18341659364248</v>
       </c>
       <c r="H152" t="n">
-        <v>8.996177174521396</v>
+        <v>183.997094408346</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>83.99582077791536</v>
       </c>
       <c r="J152" t="n">
-        <v>8.996177174521396</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K152" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C153" t="n">
-        <v>1.772333773788786</v>
+        <v>114.9620939523663</v>
       </c>
       <c r="D153" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E153" t="n">
-        <v>1.521537793993734</v>
+        <v>85.74291075174541</v>
       </c>
       <c r="F153" t="n">
-        <v>30.23034750990276</v>
+        <v>262.7193286077312</v>
       </c>
       <c r="G153" t="n">
-        <v>1.333702592444675</v>
+        <v>109.5033403501209</v>
       </c>
       <c r="H153" t="n">
-        <v>12.83439273343519</v>
+        <v>262.7193286077312</v>
       </c>
       <c r="I153" t="n">
-        <v>1.546506937169285</v>
+        <v>100.6326677724475</v>
       </c>
       <c r="J153" t="n">
-        <v>12.83439273343519</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K153" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C154" t="n">
-        <v>11.61172254966058</v>
+        <v>192.7523347517601</v>
       </c>
       <c r="D154" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E154" t="n">
-        <v>11.26551958153978</v>
+        <v>169.6087386462388</v>
       </c>
       <c r="F154" t="n">
-        <v>30.23034750990276</v>
+        <v>305.5216950259997</v>
       </c>
       <c r="G154" t="n">
-        <v>11.23686975028846</v>
+        <v>187.1776012678096</v>
       </c>
       <c r="H154" t="n">
-        <v>14.92128356441481</v>
+        <v>305.5216950259997</v>
       </c>
       <c r="I154" t="n">
-        <v>11.52270398582705</v>
+        <v>184.4874187592471</v>
       </c>
       <c r="J154" t="n">
-        <v>14.92128356441481</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K154" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C155" t="n">
-        <v>11.61172254966058</v>
+        <v>218.2947436173756</v>
       </c>
       <c r="D155" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E155" t="n">
-        <v>11.26551958153978</v>
+        <v>210.9234211709372</v>
       </c>
       <c r="F155" t="n">
-        <v>30.23034750990276</v>
+        <v>331.8698213388956</v>
       </c>
       <c r="G155" t="n">
-        <v>11.23686975028846</v>
+        <v>216.3484004122658</v>
       </c>
       <c r="H155" t="n">
-        <v>16.205924293821</v>
+        <v>331.8698213388956</v>
       </c>
       <c r="I155" t="n">
-        <v>11.52270398582705</v>
+        <v>213.1718322039249</v>
       </c>
       <c r="J155" t="n">
-        <v>16.205924293821</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K155" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C156" t="n">
-        <v>11.15234236104132</v>
+        <v>216.0656287105702</v>
       </c>
       <c r="D156" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E156" t="n">
-        <v>10.66504680606529</v>
+        <v>211.065510775805</v>
       </c>
       <c r="F156" t="n">
-        <v>30.23034750990276</v>
+        <v>349.5634898849344</v>
       </c>
       <c r="G156" t="n">
-        <v>10.64208918397388</v>
+        <v>215.8160537378888</v>
       </c>
       <c r="H156" t="n">
-        <v>17.06860450860841</v>
+        <v>349.5634898849344</v>
       </c>
       <c r="I156" t="n">
-        <v>11.13752874196805</v>
+        <v>211.2031277102809</v>
       </c>
       <c r="J156" t="n">
-        <v>17.06860450860841</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K156" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -6237,182 +6237,182 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>619.5123239502191</v>
+        <v>8.996177174521396</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>183.997094408346</v>
+        <v>8.996177174521396</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>183.997094408346</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K157" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>1.558514726823401</v>
       </c>
       <c r="D158" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1.291657873410597</v>
       </c>
       <c r="F158" t="n">
-        <v>619.5123239502191</v>
+        <v>12.83439273343519</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1.420967832295894</v>
       </c>
       <c r="H158" t="n">
-        <v>262.7193286077312</v>
+        <v>12.83439273343519</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>1.33635073415118</v>
       </c>
       <c r="J158" t="n">
-        <v>262.7193286077312</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K158" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>11.16215183371974</v>
       </c>
       <c r="D159" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>11.10292688996266</v>
       </c>
       <c r="F159" t="n">
-        <v>619.5123239502191</v>
+        <v>14.92128356441481</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>11.14723333043126</v>
       </c>
       <c r="H159" t="n">
-        <v>305.5216950259997</v>
+        <v>14.92128356441481</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>11.0968764218883</v>
       </c>
       <c r="J159" t="n">
-        <v>305.5216950259997</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K159" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>11.16215183371974</v>
       </c>
       <c r="D160" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>11.10292688996266</v>
       </c>
       <c r="F160" t="n">
-        <v>619.5123239502191</v>
+        <v>16.205924293821</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>11.14723333043126</v>
       </c>
       <c r="H160" t="n">
-        <v>331.8698213388956</v>
+        <v>16.205924293821</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>11.0968764218883</v>
       </c>
       <c r="J160" t="n">
-        <v>331.8698213388956</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K160" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>11.08122721682551</v>
       </c>
       <c r="D161" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>10.37935990411719</v>
       </c>
       <c r="F161" t="n">
-        <v>619.5123239502191</v>
+        <v>17.06860450860841</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>11.0944227992329</v>
       </c>
       <c r="H161" t="n">
-        <v>349.5634898849344</v>
+        <v>17.06860450860841</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>10.49796868462621</v>
       </c>
       <c r="J161" t="n">
-        <v>349.5634898849344</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K161" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
@@ -6422,34 +6422,34 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>30.23034750990276</v>
+        <v>183.997094408346</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>8.996177174521396</v>
+        <v>183.997094408346</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>8.996177174521396</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K162" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -6459,34 +6459,34 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>30.23034750990276</v>
+        <v>262.7193286077312</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>12.83439273343519</v>
+        <v>262.7193286077312</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>12.83439273343519</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K163" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
@@ -6496,34 +6496,34 @@
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>30.23034750990276</v>
+        <v>305.5216950259997</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>14.92128356441481</v>
+        <v>305.5216950259997</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>14.92128356441481</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K164" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
@@ -6533,34 +6533,34 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>30.23034750990276</v>
+        <v>331.8698213388956</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>16.205924293821</v>
+        <v>331.8698213388956</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>16.205924293821</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K165" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
@@ -6570,404 +6570,404 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>30.23034750990276</v>
+        <v>349.5634898849344</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>17.06860450860841</v>
+        <v>349.5634898849344</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>17.06860450860841</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K166" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C167" t="n">
-        <v>42.56277051871669</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E167" t="n">
-        <v>48.95316974606528</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>619.5123239502191</v>
+        <v>8.996177174521396</v>
       </c>
       <c r="G167" t="n">
-        <v>56.15713066921719</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>619.5123239502191</v>
+        <v>8.996177174521396</v>
       </c>
       <c r="I167" t="n">
-        <v>49.80636731695265</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K167" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C168" t="n">
-        <v>42.91265715717584</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E168" t="n">
-        <v>49.35047962819456</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>619.5123239502191</v>
+        <v>12.83439273343519</v>
       </c>
       <c r="G168" t="n">
-        <v>56.58802981241607</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>619.5123239502191</v>
+        <v>12.83439273343519</v>
       </c>
       <c r="I168" t="n">
-        <v>50.2084843529131</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K168" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>62.48360413852011</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E169" t="n">
-        <v>70.74996705529094</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>619.5123239502191</v>
+        <v>14.92128356441481</v>
       </c>
       <c r="G169" t="n">
-        <v>77.27265342706846</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>619.5123239502191</v>
+        <v>14.92128356441481</v>
       </c>
       <c r="I169" t="n">
-        <v>69.1024540201672</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K169" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>73.84249471738617</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E170" t="n">
-        <v>85.37882425583246</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>619.5123239502191</v>
+        <v>16.205924293821</v>
       </c>
       <c r="G170" t="n">
-        <v>92.34333757869942</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>619.5123239502191</v>
+        <v>16.205924293821</v>
       </c>
       <c r="I170" t="n">
-        <v>86.41191023660382</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K170" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>136.3398528013852</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E171" t="n">
-        <v>147.48906566374</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>619.5123239502191</v>
+        <v>17.06860450860841</v>
       </c>
       <c r="G171" t="n">
-        <v>154.8798731142768</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>619.5123239502191</v>
+        <v>17.06860450860841</v>
       </c>
       <c r="I171" t="n">
-        <v>149.2437840372713</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K171" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>6.933752643199993</v>
       </c>
       <c r="D172" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>13.23063811465014</v>
       </c>
       <c r="F172" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>6.863567276595608</v>
       </c>
       <c r="H172" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>13.36742981853478</v>
       </c>
       <c r="J172" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K172" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C173" t="n">
-        <v>0.03418344097327077</v>
+        <v>7.098910741987087</v>
       </c>
       <c r="D173" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0390185526158023</v>
+        <v>13.40814393390078</v>
       </c>
       <c r="F173" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G173" t="n">
-        <v>0.03685620666543286</v>
+        <v>7.028725375382701</v>
       </c>
       <c r="H173" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I173" t="n">
-        <v>0.03337648475057165</v>
+        <v>13.54487663446594</v>
       </c>
       <c r="J173" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K173" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C174" t="n">
-        <v>4.757825536849658</v>
+        <v>23.60837959790495</v>
       </c>
       <c r="D174" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E174" t="n">
-        <v>5.083385475796531</v>
+        <v>25.23721397645756</v>
       </c>
       <c r="F174" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G174" t="n">
-        <v>5.046022357706571</v>
+        <v>23.60860009569373</v>
       </c>
       <c r="H174" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I174" t="n">
-        <v>4.778648614010578</v>
+        <v>25.27597904896424</v>
       </c>
       <c r="J174" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K174" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C175" t="n">
-        <v>4.757825536849658</v>
+        <v>42.85097905762152</v>
       </c>
       <c r="D175" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E175" t="n">
-        <v>5.083385475796531</v>
+        <v>50.08053454415922</v>
       </c>
       <c r="F175" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G175" t="n">
-        <v>5.046022357706571</v>
+        <v>44.7093157564087</v>
       </c>
       <c r="H175" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I175" t="n">
-        <v>4.778648614010578</v>
+        <v>48.03081697089114</v>
       </c>
       <c r="J175" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K175" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C176" t="n">
-        <v>8.102531993037863</v>
+        <v>91.49414486806336</v>
       </c>
       <c r="D176" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E176" t="n">
-        <v>8.586792223835422</v>
+        <v>96.44497147277607</v>
       </c>
       <c r="F176" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G176" t="n">
-        <v>8.549953545066476</v>
+        <v>91.69452663331808</v>
       </c>
       <c r="H176" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I176" t="n">
-        <v>8.064255794976074</v>
+        <v>96.30498382058028</v>
       </c>
       <c r="J176" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K176" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6977,182 +6977,182 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K177" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>0.01831467609574821</v>
       </c>
       <c r="D178" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>0.01967644108617442</v>
       </c>
       <c r="F178" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>0.01854756521710589</v>
       </c>
       <c r="H178" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>0.02009382651160658</v>
       </c>
       <c r="J178" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K178" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>1.434532986806342</v>
       </c>
       <c r="D179" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>1.492599817044283</v>
       </c>
       <c r="F179" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1.448026878142357</v>
       </c>
       <c r="H179" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>1.434088563225369</v>
       </c>
       <c r="J179" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K179" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>1.434551710607169</v>
       </c>
       <c r="D180" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>1.492599817044283</v>
       </c>
       <c r="F180" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1.448026878142357</v>
       </c>
       <c r="H180" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>1.434088563225369</v>
       </c>
       <c r="J180" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K180" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>3.598998013239235</v>
       </c>
       <c r="D181" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>4.294277191274372</v>
       </c>
       <c r="F181" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>3.691039019222953</v>
       </c>
       <c r="H181" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>4.17253110856426</v>
       </c>
       <c r="J181" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K181" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -7162,34 +7162,34 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K182" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -7199,34 +7199,34 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K183" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -7236,34 +7236,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K184" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -7273,34 +7273,34 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K185" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -7310,34 +7310,34 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K186" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -7347,34 +7347,34 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>20.94092388997749</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>20.94092388997749</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K187" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
@@ -7384,34 +7384,34 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>30.87788999854429</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>30.87788999854429</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K188" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
@@ -7421,34 +7421,34 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>39.10386282951476</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>39.10386282951476</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K189" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
@@ -7458,34 +7458,34 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>46.14399110606944</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>46.14399110606944</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K190" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -7495,34 +7495,34 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>52.27564434148064</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>52.27564434148064</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K191" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
@@ -7532,34 +7532,34 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>1.046139462489713</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>1.046139462489713</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K192" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
@@ -7569,34 +7569,34 @@
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>1.530630512752588</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>1.530630512752588</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K193" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
@@ -7606,34 +7606,34 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>1.931699629097352</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>1.931699629097352</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K194" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
@@ -7643,34 +7643,34 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>2.274951191538807</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>2.274951191538807</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K195" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -7680,182 +7680,182 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>2.573908748947705</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>2.573908748947705</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K196" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>32.40483419807043</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E197" t="n">
-        <v>42.89808123726394</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G197" t="n">
-        <v>18.31681417540736</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>20.94092388997749</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I197" t="n">
-        <v>18.30579195471185</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>20.94092388997749</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K197" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>32.46770303607475</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E198" t="n">
-        <v>43.10747085844556</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G198" t="n">
-        <v>18.66289587297724</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>30.87788999854429</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I198" t="n">
-        <v>18.47317920381671</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>30.87788999854429</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K198" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>32.46770303607475</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E199" t="n">
-        <v>43.10747085844556</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G199" t="n">
-        <v>18.66289587297724</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>39.10386282951476</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I199" t="n">
-        <v>18.47317920381671</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>39.10386282951476</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K199" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C200" t="n">
-        <v>0.06286883800432334</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E200" t="n">
-        <v>0.2093896211816265</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G200" t="n">
-        <v>0.3460816975698818</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>46.14399110606944</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1673872491048566</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>46.14399110606944</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K200" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -7865,182 +7865,182 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>619.5123239502191</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>52.27564434148064</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>52.27564434148064</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="K201" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>28.91363013033405</v>
       </c>
       <c r="D202" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>50.25711949429798</v>
       </c>
       <c r="F202" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>34.40012573191548</v>
       </c>
       <c r="H202" t="n">
-        <v>1.046139462489713</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>35.53765623773516</v>
       </c>
       <c r="J202" t="n">
-        <v>1.046139462489713</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K202" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>29.16503868317478</v>
       </c>
       <c r="D203" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>50.63705056159066</v>
       </c>
       <c r="F203" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>34.72656024229807</v>
       </c>
       <c r="H203" t="n">
-        <v>1.530630512752588</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>35.72918901260589</v>
       </c>
       <c r="J203" t="n">
-        <v>1.530630512752588</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K203" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>29.16503868317477</v>
       </c>
       <c r="D204" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>50.63705056159066</v>
       </c>
       <c r="F204" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>34.72656024229807</v>
       </c>
       <c r="H204" t="n">
-        <v>1.931699629097352</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>35.72918901260589</v>
       </c>
       <c r="J204" t="n">
-        <v>1.931699629097352</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K204" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C205" t="n">
-        <v>0</v>
+        <v>0.2514085528407202</v>
       </c>
       <c r="D205" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>0.3799310672926785</v>
       </c>
       <c r="F205" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>0.326434510382591</v>
       </c>
       <c r="H205" t="n">
-        <v>2.274951191538807</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I205" t="n">
-        <v>0</v>
+        <v>0.191532774870724</v>
       </c>
       <c r="J205" t="n">
-        <v>2.274951191538807</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K205" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -8050,34 +8050,34 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>30.23034750990276</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>2.573908748947705</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>2.573908748947705</v>
+        <v>619.5123239502191</v>
       </c>
       <c r="K206" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -8087,32 +8087,34 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>1.547692525081249</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>1.547692525081249</v>
-      </c>
-      <c r="K207" t="inlineStr"/>
+        <v>30.23034750990276</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -8122,32 +8124,34 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>2.378377582329021</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>2.378377582329021</v>
-      </c>
-      <c r="K208" t="inlineStr"/>
+        <v>30.23034750990276</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -8157,32 +8161,34 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>2.893510341981031</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
       </c>
       <c r="J209" t="n">
-        <v>2.893510341981031</v>
-      </c>
-      <c r="K209" t="inlineStr"/>
+        <v>30.23034750990276</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -8192,32 +8198,34 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>3.246184380094171</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>3.246184380094171</v>
-      </c>
-      <c r="K210" t="inlineStr"/>
+        <v>30.23034750990276</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -8227,32 +8235,34 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>6</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>3.505580652684032</v>
+        <v>30.23034750990276</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>3.505580652684032</v>
-      </c>
-      <c r="K211" t="inlineStr"/>
+        <v>30.23034750990276</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -8268,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>6</v>
+        <v>1.547692525081249</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -8280,14 +8290,14 @@
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>1.547692525081249</v>
+        <v>6</v>
       </c>
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -8303,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>6</v>
+        <v>2.378377582329021</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -8315,14 +8325,14 @@
         <v>0</v>
       </c>
       <c r="J213" t="n">
-        <v>2.378377582329021</v>
+        <v>6</v>
       </c>
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -8338,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>6</v>
+        <v>2.893510341981031</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -8350,14 +8360,14 @@
         <v>0</v>
       </c>
       <c r="J214" t="n">
-        <v>2.893510341981031</v>
+        <v>6</v>
       </c>
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -8373,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>6</v>
+        <v>3.246184380094171</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -8385,14 +8395,14 @@
         <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>3.246184380094171</v>
+        <v>6</v>
       </c>
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -8408,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>6</v>
+        <v>3.505580652684032</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -8420,14 +8430,14 @@
         <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>3.505580652684032</v>
+        <v>6</v>
       </c>
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
@@ -8443,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>6</v>
+        <v>1.547692525081249</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -8455,14 +8465,14 @@
         <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>1.547692525081249</v>
+        <v>6</v>
       </c>
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
@@ -8478,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>6</v>
+        <v>2.378377582329021</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -8490,14 +8500,14 @@
         <v>0</v>
       </c>
       <c r="J218" t="n">
-        <v>2.378377582329021</v>
+        <v>6</v>
       </c>
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
@@ -8513,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>6</v>
+        <v>2.893510341981031</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -8525,14 +8535,14 @@
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>2.893510341981031</v>
+        <v>6</v>
       </c>
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
@@ -8548,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>6</v>
+        <v>3.246184380094171</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -8560,14 +8570,14 @@
         <v>0</v>
       </c>
       <c r="J220" t="n">
-        <v>3.246184380094171</v>
+        <v>6</v>
       </c>
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
@@ -8583,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>6</v>
+        <v>3.505580652684032</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -8595,9 +8605,184 @@
         <v>0</v>
       </c>
       <c r="J221" t="n">
+        <v>6</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>6</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1.547692525081249</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1.547692525081249</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>6</v>
+      </c>
+      <c r="K222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>47849</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>6</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2.378377582329021</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2.378377582329021</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>6</v>
+      </c>
+      <c r="K223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>49675</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>6</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2.893510341981031</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>2.893510341981031</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>6</v>
+      </c>
+      <c r="K224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>51502</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>6</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>3.246184380094171</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>3.246184380094171</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>6</v>
+      </c>
+      <c r="K225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>53328</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>6</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
         <v>3.505580652684032</v>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>3.505580652684032</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>6</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
